--- a/base_dados.xlsx
+++ b/base_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\GitHub\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E7A5AD-79A8-4FCD-90A6-F08E0ABB6A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CDE9C3-6B0E-4CFB-9790-7B04C431FFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{65BF413F-4309-4D8D-A46D-C342773C5167}"/>
   </bookViews>
@@ -3704,7 +3704,7 @@
         <v>37</v>
       </c>
       <c r="D182" s="2">
-        <v>5831.28</v>
+        <v>5831</v>
       </c>
       <c r="E182" s="1">
         <v>4984</v>
@@ -3721,7 +3721,7 @@
         <v>37</v>
       </c>
       <c r="D183" s="2">
-        <v>7063.2000000000007</v>
+        <v>7063</v>
       </c>
       <c r="E183" s="1">
         <v>6540</v>
@@ -3755,7 +3755,7 @@
         <v>37</v>
       </c>
       <c r="D185" s="2">
-        <v>9691.7999999999993</v>
+        <v>9691</v>
       </c>
       <c r="E185" s="1">
         <v>8355</v>
@@ -3772,7 +3772,7 @@
         <v>37</v>
       </c>
       <c r="D186" s="2">
-        <v>1813.56</v>
+        <v>1813</v>
       </c>
       <c r="E186" s="1">
         <v>1524</v>
@@ -3789,7 +3789,7 @@
         <v>37</v>
       </c>
       <c r="D187" s="2">
-        <v>4428.0600000000004</v>
+        <v>4428</v>
       </c>
       <c r="E187" s="1">
         <v>4866</v>
@@ -3806,7 +3806,7 @@
         <v>37</v>
       </c>
       <c r="D188" s="2">
-        <v>7652.7</v>
+        <v>7652</v>
       </c>
       <c r="E188" s="1">
         <v>8503</v>
@@ -3823,7 +3823,7 @@
         <v>37</v>
       </c>
       <c r="D189" s="2">
-        <v>6082.4000000000005</v>
+        <v>6082</v>
       </c>
       <c r="E189" s="1">
         <v>7603</v>
@@ -3840,7 +3840,7 @@
         <v>37</v>
       </c>
       <c r="D190" s="2">
-        <v>3591.9199999999996</v>
+        <v>3591</v>
       </c>
       <c r="E190" s="1">
         <v>3044</v>
@@ -3857,7 +3857,7 @@
         <v>37</v>
       </c>
       <c r="D191" s="2">
-        <v>2488.7999999999997</v>
+        <v>2488</v>
       </c>
       <c r="E191" s="1">
         <v>2074</v>
@@ -3874,7 +3874,7 @@
         <v>37</v>
       </c>
       <c r="D192" s="2">
-        <v>4992.26</v>
+        <v>4992</v>
       </c>
       <c r="E192" s="1">
         <v>5486</v>
@@ -3891,7 +3891,7 @@
         <v>37</v>
       </c>
       <c r="D193" s="2">
-        <v>2992.08</v>
+        <v>2992</v>
       </c>
       <c r="E193" s="1">
         <v>3288</v>
@@ -3925,7 +3925,7 @@
         <v>38</v>
       </c>
       <c r="D195" s="2">
-        <v>9107.84</v>
+        <v>9107</v>
       </c>
       <c r="E195" s="1">
         <v>8132</v>
@@ -3942,7 +3942,7 @@
         <v>38</v>
       </c>
       <c r="D196" s="2">
-        <v>6147.45</v>
+        <v>6147</v>
       </c>
       <c r="E196" s="1">
         <v>6471</v>
@@ -3959,7 +3959,7 @@
         <v>38</v>
       </c>
       <c r="D197" s="2">
-        <v>3856.71</v>
+        <v>3856</v>
       </c>
       <c r="E197" s="1">
         <v>4433</v>
@@ -3976,7 +3976,7 @@
         <v>38</v>
       </c>
       <c r="D198" s="2">
-        <v>1040.4000000000001</v>
+        <v>1040</v>
       </c>
       <c r="E198" s="1">
         <v>1020</v>
@@ -3993,7 +3993,7 @@
         <v>38</v>
       </c>
       <c r="D199" s="2">
-        <v>2309.04</v>
+        <v>2309</v>
       </c>
       <c r="E199" s="1">
         <v>2138</v>
@@ -4010,7 +4010,7 @@
         <v>38</v>
       </c>
       <c r="D200" s="2">
-        <v>10821.52</v>
+        <v>10821</v>
       </c>
       <c r="E200" s="1">
         <v>9928</v>
@@ -4027,7 +4027,7 @@
         <v>38</v>
       </c>
       <c r="D201" s="2">
-        <v>3250.7999999999997</v>
+        <v>3250</v>
       </c>
       <c r="E201" s="1">
         <v>3780</v>
@@ -4044,7 +4044,7 @@
         <v>38</v>
       </c>
       <c r="D202" s="2">
-        <v>3779.12</v>
+        <v>3779</v>
       </c>
       <c r="E202" s="1">
         <v>3896</v>
@@ -4061,7 +4061,7 @@
         <v>38</v>
       </c>
       <c r="D203" s="2">
-        <v>2839.2000000000003</v>
+        <v>2839</v>
       </c>
       <c r="E203" s="1">
         <v>2535</v>
@@ -4078,7 +4078,7 @@
         <v>38</v>
       </c>
       <c r="D204" s="2">
-        <v>6658.95</v>
+        <v>6658</v>
       </c>
       <c r="E204" s="1">
         <v>6465</v>
@@ -4095,7 +4095,7 @@
         <v>38</v>
       </c>
       <c r="D205" s="2">
-        <v>913.5</v>
+        <v>913</v>
       </c>
       <c r="E205" s="1">
         <v>1050</v>
@@ -4129,7 +4129,7 @@
         <v>39</v>
       </c>
       <c r="D207" s="2">
-        <v>1535.51</v>
+        <v>1535</v>
       </c>
       <c r="E207" s="1">
         <v>1583</v>
@@ -4146,7 +4146,7 @@
         <v>39</v>
       </c>
       <c r="D208" s="2">
-        <v>2472.48</v>
+        <v>2472</v>
       </c>
       <c r="E208" s="1">
         <v>2424</v>
@@ -4163,7 +4163,7 @@
         <v>39</v>
       </c>
       <c r="D209" s="2">
-        <v>9254.74</v>
+        <v>9254</v>
       </c>
       <c r="E209" s="1">
         <v>7843</v>
@@ -4180,7 +4180,7 @@
         <v>39</v>
       </c>
       <c r="D210" s="2">
-        <v>6867.12</v>
+        <v>6867</v>
       </c>
       <c r="E210" s="1">
         <v>7384</v>
@@ -4197,7 +4197,7 @@
         <v>39</v>
       </c>
       <c r="D211" s="2">
-        <v>2142.5600000000004</v>
+        <v>2142</v>
       </c>
       <c r="E211" s="1">
         <v>1913</v>
@@ -4214,7 +4214,7 @@
         <v>39</v>
       </c>
       <c r="D212" s="2">
-        <v>3662.4</v>
+        <v>3662</v>
       </c>
       <c r="E212" s="1">
         <v>3360</v>
@@ -4231,7 +4231,7 @@
         <v>39</v>
       </c>
       <c r="D213" s="2">
-        <v>5768.88</v>
+        <v>5768</v>
       </c>
       <c r="E213" s="1">
         <v>6708</v>
@@ -4248,7 +4248,7 @@
         <v>39</v>
       </c>
       <c r="D214" s="2">
-        <v>6049.86</v>
+        <v>6049</v>
       </c>
       <c r="E214" s="1">
         <v>5127</v>
@@ -4265,7 +4265,7 @@
         <v>39</v>
       </c>
       <c r="D215" s="2">
-        <v>1481.04</v>
+        <v>1481</v>
       </c>
       <c r="E215" s="1">
         <v>1496</v>
@@ -4282,7 +4282,7 @@
         <v>39</v>
       </c>
       <c r="D216" s="2">
-        <v>3163.5000000000005</v>
+        <v>3163</v>
       </c>
       <c r="E216" s="1">
         <v>2850</v>
@@ -4299,7 +4299,7 @@
         <v>39</v>
       </c>
       <c r="D217" s="2">
-        <v>5878.5999999999995</v>
+        <v>5878</v>
       </c>
       <c r="E217" s="1">
         <v>6188</v>
